--- a/CONTROL_PROYECTOS_FINAL.xlsx
+++ b/CONTROL_PROYECTOS_FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pmpconsultoria.sharepoint.com/sites/PMP-Sigral-S_Integrado_SIG/Shared Documents/S_Integrado_(SIG)/2_Gestión_SIG/Registros/9.Control_Proyectos/9.7.Conformidad del Servicio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{0AE463AB-DDB3-4984-966B-3D3B7CED8A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B231D838-A6E4-48B2-951F-E8EBFC64FB3B}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{0AE463AB-DDB3-4984-966B-3D3B7CED8A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33D2115F-F17C-49F8-83BA-5AD1C4CC7907}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4026,7 +4026,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y185"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4224,7 +4223,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7"/>
@@ -4257,7 +4256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>2026</v>
       </c>
@@ -4318,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2026</v>
       </c>
@@ -4391,7 +4390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>2026</v>
       </c>
@@ -4462,7 +4461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>2026</v>
       </c>
@@ -4521,7 +4520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>2026</v>
       </c>
@@ -4576,7 +4575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>2026</v>
       </c>
@@ -4649,7 +4648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19">
         <v>2026</v>
       </c>
@@ -4718,7 +4717,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>2026</v>
       </c>
@@ -4787,7 +4786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19">
         <v>2026</v>
       </c>
@@ -4925,7 +4924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19">
         <v>2026</v>
       </c>
@@ -4998,7 +4997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>2026</v>
       </c>
@@ -5067,7 +5066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19">
         <v>2026</v>
       </c>
@@ -5140,7 +5139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>2026</v>
       </c>
@@ -5209,7 +5208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="19">
         <v>2026</v>
       </c>
@@ -5286,7 +5285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>2026</v>
       </c>
@@ -5361,7 +5360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="19">
         <v>2026</v>
       </c>
@@ -5505,7 +5504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="19">
         <v>2026</v>
       </c>
@@ -5576,7 +5575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>2026</v>
       </c>
@@ -5645,7 +5644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="19">
         <v>2026</v>
       </c>
@@ -5722,7 +5721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>2026</v>
       </c>
@@ -5793,7 +5792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="19">
         <v>2026</v>
       </c>
@@ -5868,7 +5867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>2026</v>
       </c>
@@ -5945,7 +5944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="19">
         <v>2026</v>
       </c>
@@ -6020,7 +6019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>2026</v>
       </c>
@@ -6085,7 +6084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="19">
         <v>2026</v>
       </c>
@@ -6160,7 +6159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>2025</v>
       </c>
@@ -6231,7 +6230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="19">
         <v>2025</v>
       </c>
@@ -6306,7 +6305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>2026</v>
       </c>
@@ -6373,7 +6372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="19">
         <v>2025</v>
       </c>
@@ -6519,7 +6518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="19">
         <v>2026</v>
       </c>
@@ -6586,7 +6585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>2025</v>
       </c>
@@ -6659,7 +6658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="19">
         <v>2025</v>
       </c>
@@ -6734,7 +6733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>2026</v>
       </c>
@@ -6878,7 +6877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>2025</v>
       </c>
@@ -6955,7 +6954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="19">
         <v>2025</v>
       </c>
@@ -7030,7 +7029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>2026</v>
       </c>
@@ -7107,7 +7106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="19">
         <v>2025</v>
       </c>
@@ -7180,7 +7179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>2025</v>
       </c>
@@ -7255,7 +7254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="19">
         <v>2025</v>
       </c>
@@ -7334,7 +7333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>2025</v>
       </c>
@@ -7411,7 +7410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="19">
         <v>2025</v>
       </c>
@@ -7488,7 +7487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>2025</v>
       </c>
@@ -7565,7 +7564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="19">
         <v>2025</v>
       </c>
@@ -7640,7 +7639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>2025</v>
       </c>
@@ -7715,7 +7714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="19">
         <v>2026</v>
       </c>
@@ -7788,7 +7787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>2025</v>
       </c>
@@ -7865,7 +7864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="19">
         <v>2025</v>
       </c>
@@ -7944,7 +7943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>2026</v>
       </c>
@@ -8017,7 +8016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="19">
         <v>2026</v>
       </c>
@@ -8090,7 +8089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>2025</v>
       </c>
@@ -8167,7 +8166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="19">
         <v>2026</v>
       </c>
@@ -8240,7 +8239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>2025</v>
       </c>
@@ -8317,7 +8316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="19">
         <v>2025</v>
       </c>
@@ -8390,7 +8389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>2026</v>
       </c>
@@ -8467,7 +8466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="19">
         <v>2025</v>
       </c>
@@ -8546,7 +8545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>2025</v>
       </c>
@@ -8623,7 +8622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="19">
         <v>2025</v>
       </c>
@@ -8698,7 +8697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>2025</v>
       </c>
@@ -8777,7 +8776,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="19">
         <v>2025</v>
       </c>
@@ -8854,7 +8853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>2025</v>
       </c>
@@ -8931,7 +8930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="19">
         <v>2026</v>
       </c>
@@ -9008,7 +9007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>2026</v>
       </c>
@@ -9083,7 +9082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="19">
         <v>2025</v>
       </c>
@@ -9160,7 +9159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>2025</v>
       </c>
@@ -9237,7 +9236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="19">
         <v>2026</v>
       </c>
@@ -9308,7 +9307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>2025</v>
       </c>
@@ -9464,7 +9463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>2026</v>
       </c>
@@ -9537,7 +9536,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="19">
         <v>2025</v>
       </c>
@@ -9616,7 +9615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>2025</v>
       </c>
@@ -9770,7 +9769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>2025</v>
       </c>
@@ -9847,7 +9846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="19">
         <v>2025</v>
       </c>
@@ -9926,7 +9925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>2025</v>
       </c>
@@ -10005,7 +10004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="19">
         <v>2026</v>
       </c>
@@ -10084,7 +10083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>2025</v>
       </c>
@@ -10161,7 +10160,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="19">
         <v>2025</v>
       </c>
@@ -10238,7 +10237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>2025</v>
       </c>
@@ -10317,7 +10316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="19">
         <v>2025</v>
       </c>
@@ -10396,7 +10395,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>2024</v>
       </c>
@@ -10475,7 +10474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="19">
         <v>2024</v>
       </c>
@@ -10552,7 +10551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>2025</v>
       </c>
@@ -10631,7 +10630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="19">
         <v>2026</v>
       </c>
@@ -10704,7 +10703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>2024</v>
       </c>
@@ -10783,7 +10782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="19">
         <v>2024</v>
       </c>
@@ -10860,7 +10859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>2024</v>
       </c>
@@ -10935,7 +10934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="19">
         <v>2024</v>
       </c>
@@ -11012,7 +11011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>2024</v>
       </c>
@@ -11089,7 +11088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="19">
         <v>2024</v>
       </c>
@@ -11166,7 +11165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>2024</v>
       </c>
@@ -11243,7 +11242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="19">
         <v>2025</v>
       </c>
@@ -11322,7 +11321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>2025</v>
       </c>
@@ -11401,7 +11400,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="19">
         <v>2025</v>
       </c>
@@ -11480,7 +11479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>2025</v>
       </c>
@@ -11559,7 +11558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="19">
         <v>2025</v>
       </c>
@@ -11638,7 +11637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>2024</v>
       </c>
@@ -11717,7 +11716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="19">
         <v>2024</v>
       </c>
@@ -11772,7 +11771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>2024</v>
       </c>
@@ -11851,7 +11850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="19">
         <v>2025</v>
       </c>
@@ -11930,7 +11929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>2024</v>
       </c>
@@ -12005,7 +12004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="19">
         <v>2024</v>
       </c>
@@ -12082,7 +12081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>2025</v>
       </c>
@@ -12159,7 +12158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="19">
         <v>2026</v>
       </c>
@@ -12230,7 +12229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>2025</v>
       </c>
@@ -12309,7 +12308,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="19">
         <v>2025</v>
       </c>
@@ -12378,7 +12377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>2024</v>
       </c>
@@ -12457,7 +12456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="19">
         <v>2024</v>
       </c>
@@ -12536,7 +12535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>2024</v>
       </c>
@@ -12615,7 +12614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="19">
         <v>2024</v>
       </c>
@@ -12692,7 +12691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>2024</v>
       </c>
@@ -12769,7 +12768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="19">
         <v>2025</v>
       </c>
@@ -12846,7 +12845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>2024</v>
       </c>
@@ -12925,7 +12924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="19">
         <v>2024</v>
       </c>
@@ -13081,7 +13080,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="19">
         <v>2025</v>
       </c>
@@ -13160,7 +13159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>2025</v>
       </c>
@@ -13239,7 +13238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="19">
         <v>2025</v>
       </c>
@@ -13318,7 +13317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>2024</v>
       </c>
@@ -13395,7 +13394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="19">
         <v>2024</v>
       </c>
@@ -13470,7 +13469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>2024</v>
       </c>
@@ -13549,7 +13548,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="19">
         <v>2024</v>
       </c>
@@ -13628,7 +13627,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>2025</v>
       </c>
@@ -13705,7 +13704,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="19">
         <v>2025</v>
       </c>
@@ -13784,7 +13783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>2024</v>
       </c>
@@ -13861,7 +13860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="19">
         <v>2025</v>
       </c>
@@ -13938,7 +13937,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>2024</v>
       </c>
@@ -14015,7 +14014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="19">
         <v>2025</v>
       </c>
@@ -14094,7 +14093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>2024</v>
       </c>
@@ -14169,7 +14168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="19">
         <v>2024</v>
       </c>
@@ -14248,7 +14247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>2024</v>
       </c>
@@ -14327,7 +14326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="19">
         <v>2024</v>
       </c>
@@ -14406,7 +14405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>2024</v>
       </c>
@@ -14485,7 +14484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="19">
         <v>2024</v>
       </c>
@@ -14558,7 +14557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>2024</v>
       </c>
@@ -14635,7 +14634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="19">
         <v>2024</v>
       </c>
@@ -14714,7 +14713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>2024</v>
       </c>
@@ -14791,7 +14790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="19">
         <v>2024</v>
       </c>
@@ -14868,7 +14867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>2025</v>
       </c>
@@ -14945,7 +14944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="19">
         <v>2025</v>
       </c>
@@ -15099,7 +15098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="19">
         <v>2025</v>
       </c>
@@ -15174,7 +15173,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>2026</v>
       </c>
@@ -15235,7 +15234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="19">
         <v>2026</v>
       </c>
@@ -15304,7 +15303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>2026</v>
       </c>
@@ -15373,7 +15372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="19">
         <v>2026</v>
       </c>
@@ -15440,7 +15439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>2024</v>
       </c>
@@ -15517,7 +15516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="19">
         <v>2024</v>
       </c>
@@ -15594,7 +15593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>2024</v>
       </c>
@@ -15673,7 +15672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="19">
         <v>2025</v>
       </c>
@@ -15752,7 +15751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>2025</v>
       </c>
@@ -15825,7 +15824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="19">
         <v>2024</v>
       </c>
@@ -15977,7 +15976,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="19">
         <v>2024</v>
       </c>
@@ -16131,7 +16130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="19">
         <v>2026</v>
       </c>
@@ -16210,7 +16209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>2025</v>
       </c>
@@ -16289,7 +16288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="19">
         <v>2024</v>
       </c>
@@ -16366,7 +16365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>2024</v>
       </c>
@@ -16443,7 +16442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="19">
         <v>2024</v>
       </c>
@@ -16597,7 +16596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="19">
         <v>2024</v>
       </c>
@@ -16676,7 +16675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>2024</v>
       </c>
@@ -16753,7 +16752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="19">
         <v>2024</v>
       </c>
@@ -16832,7 +16831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>2024</v>
       </c>
@@ -16911,7 +16910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="19">
         <v>2024</v>
       </c>
@@ -16990,7 +16989,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="5">
         <v>2024</v>
       </c>
@@ -17067,7 +17066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="19">
         <v>2024</v>
       </c>
@@ -17209,7 +17208,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="19">
         <v>2024</v>
       </c>
@@ -17282,7 +17281,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="5">
         <v>2024</v>
       </c>
@@ -17361,7 +17360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="19">
         <v>2024</v>
       </c>
@@ -17440,7 +17439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="5">
         <v>2024</v>
       </c>
@@ -17515,7 +17514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="19">
         <v>2024</v>
       </c>
@@ -17594,7 +17593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="5">
         <v>2024</v>
       </c>
@@ -17671,7 +17670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="19">
         <v>2024</v>
       </c>
@@ -17750,7 +17749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="5">
         <v>2024</v>
       </c>
@@ -17830,13 +17829,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:W185" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="A. Ferrer"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A4:W185" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="6">
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A2:W2"/>
@@ -19511,25 +19504,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ff59c9f8-adb4-49df-b682-ac5612a0c8e7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F532CF243A89247AB3C7C7FE358C0F1" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3551982f1de60e7bb6b3a145eb4387b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ff59c9f8-adb4-49df-b682-ac5612a0c8e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="095247d6cb34483703ce062d15864647" ns2:_="">
     <xsd:import namespace="ff59c9f8-adb4-49df-b682-ac5612a0c8e7"/>
@@ -19719,12 +19693,39 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ff59c9f8-adb4-49df-b682-ac5612a0c8e7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE9E4C8-2FCF-4495-894E-F57ABDA5B001}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F7FB27A-8A8C-45CD-B33E-9BA9A960B187}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ff59c9f8-adb4-49df-b682-ac5612a0c8e7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ff59c9f8-adb4-49df-b682-ac5612a0c8e7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19738,5 +19739,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F7FB27A-8A8C-45CD-B33E-9BA9A960B187}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE9E4C8-2FCF-4495-894E-F57ABDA5B001}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ff59c9f8-adb4-49df-b682-ac5612a0c8e7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>